--- a/data/115學年度餐點整合明細-202609.xlsx
+++ b/data/115學年度餐點整合明細-202609.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="266">
   <si>
     <t xml:space="preserve">臺北市大安區龍安國小暨附設幼兒園 115學年度9月份全日餐點一覽表</t>
   </si>
@@ -792,37 +792,7 @@
     <t xml:space="preserve">提供天數</t>
   </si>
   <si>
-    <t xml:space="preserve">營養亮點</t>
-  </si>
-  <si>
-    <t xml:space="preserve">富含鉀離子、水溶性膳食纖維，助消化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">超高維生素C抗氧化，低GI水果首選</t>
-  </si>
-  <si>
-    <t xml:space="preserve">奇異果酵素、高維生素C與葉酸</t>
-  </si>
-  <si>
-    <t xml:space="preserve">鳳梨酵素助蛋白質分解與胃腸消化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">清涼消暑、水分充沛、含茄紅素</t>
-  </si>
-  <si>
-    <t xml:space="preserve">富含多酚、花青素與天然葡萄糖</t>
-  </si>
-  <si>
-    <t xml:space="preserve">豐富果膠與槲皮素，溫和養胃</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高甜菜紅素與水溶性纖維促進排便</t>
-  </si>
-  <si>
     <t xml:space="preserve">合計提供天數</t>
-  </si>
-  <si>
-    <t xml:space="preserve">每日均提供 1 份新鮮水果</t>
   </si>
   <si>
     <t xml:space="preserve">幼兒園早午點心型態分佈</t>
@@ -869,7 +839,7 @@
     <numFmt numFmtId="167" formatCode="General"/>
     <numFmt numFmtId="168" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -973,26 +943,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1016,13 +966,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8C5B3E"/>
-        <bgColor rgb="FFAB4744"/>
+        <bgColor rgb="FFB85D19"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAF2EC"/>
-        <bgColor rgb="FFF9F9F9"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1090,7 +1040,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1135,6 +1085,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1144,15 +1098,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1160,7 +1114,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1168,15 +1122,15 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1188,7 +1142,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1213,17 +1167,17 @@
       <rgbColor rgb="FF800000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF777777"/>
+      <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF8C5B3E"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF4A7C59"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF878787"/>
-      <rgbColor rgb="FF93A9CE"/>
-      <rgbColor rgb="FFAB4744"/>
-      <rgbColor rgb="FFF9F9F9"/>
       <rgbColor rgb="FFEAF2EC"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFDC853E"/>
+      <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFD0D7D1"/>
       <rgbColor rgb="FF000080"/>
@@ -1232,893 +1186,35 @@
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF4F81BD"/>
+      <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFD09493"/>
-      <rgbColor rgb="FF777777"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF4672A8"/>
+      <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF9BBB59"/>
+      <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF725990"/>
-      <rgbColor rgb="FF8AA64F"/>
+      <rgbColor rgb="FF555555"/>
+      <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF2D5A43"/>
-      <rgbColor rgb="FF4299B0"/>
+      <rgbColor rgb="FF4A7C59"/>
       <rgbColor rgb="FF1E4D2B"/>
       <rgbColor rgb="FF222222"/>
       <rgbColor rgb="FFB85D19"/>
-      <rgbColor rgb="FFC0504D"/>
-      <rgbColor rgb="FF555555"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1E3D2F"/>
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:plotArea>
-      <c:pieChart>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>營養與食材分析!B13</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>供應次數</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:explosion val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="4f81bd"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="c0504d"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="9bbb59"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="bestFit"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="bestFit"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="0"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>營養與食材分析!$A$14:$A$16</c:f>
-              <c:strCache>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>雞肉料理</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>豬肉料理</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>魚肉海鮮</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>營養與食材分析!$B$14:$B$16</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:firstSliceAng val="0"/>
-      </c:pieChart>
-      <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="ffffff"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:chart>
-    <c:plotArea>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="1"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>營養與食材分析!$B$29:$B$29</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>提供天數</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="4f81bd"/>
-            </a:solidFill>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="f9f9f9"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="4672a8"/>
-              </a:solidFill>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="f9f9f9"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="ab4744"/>
-              </a:solidFill>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="f9f9f9"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="8aa64f"/>
-              </a:solidFill>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="f9f9f9"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="3"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="725990"/>
-              </a:solidFill>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="f9f9f9"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="4"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="4299b0"/>
-              </a:solidFill>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="f9f9f9"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="dc853e"/>
-              </a:solidFill>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="f9f9f9"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="6"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="93a9ce"/>
-              </a:solidFill>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="f9f9f9"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="7"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="d09493"/>
-              </a:solidFill>
-              <a:ln w="9360">
-                <a:solidFill>
-                  <a:srgbClr val="f9f9f9"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:dLbl>
-              <c:idx val="0"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="1"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="2"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="3"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="4"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="5"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="6"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:txPr>
-                <a:bodyPr/>
-                <a:lstStyle/>
-                <a:p>
-                  <a:pPr>
-                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                      <a:solidFill>
-                        <a:srgbClr val="000000"/>
-                      </a:solidFill>
-                      <a:latin typeface="Arial"/>
-                    </a:defRPr>
-                  </a:pPr>
-                </a:p>
-              </c:txPr>
-              <c:dLblPos val="outEnd"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="0"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:separator>; </c:separator>
-            </c:dLbl>
-            <c:txPr>
-              <a:bodyPr/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:separator>; </c:separator>
-            <c:showLeaderLines val="0"/>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>營養與食材分析!$A$30:$A$37</c:f>
-              <c:strCache>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>香蕉</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>芭樂</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>奇異果</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>鳳梨</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>西瓜</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>葡萄</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>蘋果</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>火龍果</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>營養與食材分析!$B$30:$B$37</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-        </c:ser>
-        <c:gapWidth val="150"/>
-        <c:overlap val="0"/>
-        <c:axId val="29460439"/>
-        <c:axId val="35013550"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="29460439"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>水果品項</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="35013550"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="35013550"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>天數 (次)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="29460439"/>
-        <c:crosses val="autoZero"/>
-      </c:valAx>
-      <c:spPr>
-        <a:solidFill>
-          <a:srgbClr val="ffffff"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="ffffff"/>
-    </a:solidFill>
-    <a:ln>
-      <a:noFill/>
-    </a:ln>
-  </c:spPr>
-</c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2131,71 +1227,6 @@
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>360</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>819000</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>11520</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="5786640" y="571680"/>
-        <a:ext cx="5762520" cy="3059280"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>360</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>819000</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>64440</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 2"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="5786640" y="4280040"/>
-        <a:ext cx="5762520" cy="3239280"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4533,12 +3564,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1048576"/>
-  <sheetFormatPr defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I46"/>
+  <sheetFormatPr defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="31.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="5" style="1" width="12.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1025" min="11" style="1" width="7.52"/>
@@ -4571,65 +3602,65 @@
       <c r="I2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="11"/>
+      <c r="B4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="14" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="15" t="n">
         <v>712.76</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>716</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>784</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>649</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
@@ -4643,305 +3674,318 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="18" t="n">
         <f aca="false">B14/$B$17</f>
         <v>0.476190476190476</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C15" s="17" t="n">
+      <c r="C15" s="18" t="n">
         <f aca="false">B15/$B$17</f>
         <v>0.476190476190476</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="18" t="n">
         <f aca="false">B16/$B$17</f>
         <v>0.0476190476190476</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="B17" s="19" t="n">
+      <c r="B17" s="20" t="n">
         <f aca="false">SUM(B14:B16)</f>
         <v>21</v>
       </c>
-      <c r="C17" s="20" t="n">
+      <c r="C17" s="21" t="n">
         <f aca="false">SUM(C14:C16)</f>
         <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="B19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="0"/>
     </row>
     <row r="20" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="B20" s="21" t="n">
+      <c r="B20" s="22" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="22" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="B22" s="21" t="n">
+      <c r="B22" s="22" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="B23" s="21" t="n">
+      <c r="B23" s="22" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="B24" s="21" t="n">
+      <c r="B24" s="22" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="B25" s="21" t="n">
+      <c r="B25" s="22" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="B26" s="21" t="n">
+      <c r="B26" s="22" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="B27" s="21" t="n">
+      <c r="B27" s="22" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="s">
+    <row r="28" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="17"/>
+      <c r="B28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="B28" s="22"/>
-      <c r="C28" s="22"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B30" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C30" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="18" t="n">
+        <f aca="false">B31/$B$39</f>
+        <v>0.238095238095238</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="18" t="n">
+        <f aca="false">B32/$B$39</f>
+        <v>0.19047619047619</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="18" t="n">
+        <f aca="false">B33/$B$39</f>
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="18" t="n">
+        <f aca="false">B34/$B$39</f>
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="18" t="n">
+        <f aca="false">B35/$B$39</f>
+        <v>0.0952380952380952</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="18" t="n">
+        <f aca="false">B36/$B$39</f>
+        <v>0.0952380952380952</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="18" t="n">
+        <f aca="false">B37/$B$39</f>
+        <v>0.0476190476190476</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B38" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="18" t="n">
+        <f aca="false">B38/$B$39</f>
+        <v>0.0476190476190476</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="C30" s="24" t="s">
+      <c r="B39" s="20" t="n">
+        <f aca="false">SUM(B31:B38)</f>
+        <v>21</v>
+      </c>
+      <c r="C39" s="21" t="n">
+        <f aca="false">SUM(C31:C38)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="23" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="24" t="s">
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+    </row>
+    <row r="42" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="21" t="n">
+      <c r="B42" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="B43" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="B44" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="B45" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="B46" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="24" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C33" s="24" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="24" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B35" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="B36" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="22" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="B38" s="19" t="n">
-        <f aca="false">SUM(B30:B37)</f>
-        <v>21</v>
-      </c>
-      <c r="C38" s="18" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="22" t="s">
+      <c r="C46" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-    </row>
-    <row r="41" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="B41" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="C41" s="24" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="B42" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="C42" s="24" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="B43" s="21" t="n">
-        <v>10</v>
-      </c>
-      <c r="C43" s="24" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="B44" s="21" t="n">
-        <v>8</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="B45" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A1:I1"/>
@@ -4949,8 +3993,8 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A41:C41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
@@ -4959,6 +4003,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>